--- a/data/trans_dic/AIRE_1_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/AIRE_1_R-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>59,67; 71,33</t>
+          <t>59,67; 71,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>60,23; 71,01</t>
+          <t>59,69; 70,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61,49; 69,71</t>
+          <t>61,21; 69,66</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>62,84; 74,5</t>
+          <t>62,81; 74,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>73,56; 83,46</t>
+          <t>73,47; 83,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68,59; 76,68</t>
+          <t>68,9; 77,2</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72,21; 82,91</t>
+          <t>71,65; 83,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74,19; 87,33</t>
+          <t>72,86; 87,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73,76; 83,04</t>
+          <t>74,11; 82,93</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>72,57; 81,62</t>
+          <t>71,93; 81,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>72,67; 93,05</t>
+          <t>72,73; 92,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>74,75; 89,24</t>
+          <t>74,7; 89,36</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>75,19; 86,15</t>
+          <t>75,47; 86,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>54,71; 84,09</t>
+          <t>54,9; 84,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65,29; 83,22</t>
+          <t>63,56; 83,41</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>46,61; 77,84</t>
+          <t>46,12; 78,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>74,35; 82,73</t>
+          <t>74,15; 82,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>70,49; 80,01</t>
+          <t>69,93; 79,55</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>71,26; 76,02</t>
+          <t>71,17; 76,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>73,96; 85,11</t>
+          <t>73,82; 84,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73,48; 80,19</t>
+          <t>73,68; 80,25</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>158006; 188863</t>
+          <t>157995; 189152</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>129150; 152273</t>
+          <t>127997; 151780</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>294690; 334075</t>
+          <t>293345; 333843</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>162496; 192658</t>
+          <t>162428; 192357</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>135494; 153727</t>
+          <t>135320; 153747</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>303697; 339523</t>
+          <t>305069; 341847</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>163094; 187254</t>
+          <t>161810; 187484</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>60499; 71208</t>
+          <t>59412; 71213</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>226740; 255250</t>
+          <t>227810; 254932</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>385599; 433696</t>
+          <t>382183; 431230</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>433094; 554599</t>
+          <t>433453; 550875</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>842660; 1005995</t>
+          <t>842106; 1007388</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>173021; 198250</t>
+          <t>173672; 198171</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>211422; 324968</t>
+          <t>212150; 324999</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>402540; 513093</t>
+          <t>391916; 514274</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>51572; 86120</t>
+          <t>51025; 87362</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>307277; 341931</t>
+          <t>306463; 341509</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>369295; 419193</t>
+          <t>366408; 416788</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1155282; 1232459</t>
+          <t>1153854; 1232206</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1387335; 1596533</t>
+          <t>1384781; 1580876</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2569872; 2804330</t>
+          <t>2576781; 2806557</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/AIRE_1_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/AIRE_1_R-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>64,76%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>59,67; 71,44</t>
+          <t>57,45; 69,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>59,69; 70,78</t>
+          <t>59,83; 70,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61,21; 69,66</t>
+          <t>60,55; 68,44</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,62%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>62,81; 74,38</t>
+          <t>61,73; 73,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>73,47; 83,47</t>
+          <t>73,2; 83,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68,9; 77,2</t>
+          <t>68,49; 76,55</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>79,3%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>71,65; 83,01</t>
+          <t>72,2; 83,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>72,86; 87,33</t>
+          <t>74,04; 87,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74,11; 82,93</t>
+          <t>74,47; 83,14</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>76,59%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>71,93; 81,16</t>
+          <t>73,94; 81,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>72,73; 92,43</t>
+          <t>70,81; 78,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>74,7; 89,36</t>
+          <t>73,37; 79,11</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>82,41%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>75,47; 86,12</t>
+          <t>75,65; 85,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>54,9; 84,1</t>
+          <t>79,01; 85,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63,56; 83,41</t>
+          <t>79,31; 84,86</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>76,53%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>46,12; 78,96</t>
+          <t>50,14; 79,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>74,15; 82,63</t>
+          <t>75,38; 82,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69,93; 79,55</t>
+          <t>71,7; 80,42</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>75,69%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>71,17; 76,0</t>
+          <t>71,34; 76,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>73,82; 84,27</t>
+          <t>75,46; 78,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73,68; 80,25</t>
+          <t>74,28; 77,13</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>173981</t>
+          <t>183869</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>140768</t>
+          <t>153244</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>314749</t>
+          <t>337113</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>157995; 189152</t>
+          <t>163894; 198406</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>127997; 151780</t>
+          <t>140776; 166260</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>293345; 333843</t>
+          <t>315196; 356313</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>177963</t>
+          <t>185183</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>145362</t>
+          <t>159226</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>323325</t>
+          <t>344410</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>162428; 192357</t>
+          <t>167965; 200213</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>135320; 153747</t>
+          <t>148010; 167813</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>305069; 341847</t>
+          <t>324862; 363077</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>176039</t>
+          <t>197410</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>66310</t>
+          <t>75444</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>242349</t>
+          <t>272854</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>161810; 187484</t>
+          <t>181372; 209455</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>59412; 71213</t>
+          <t>68741; 80845</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>227810; 254932</t>
+          <t>256207; 286046</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>411210</t>
+          <t>444248</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>493495</t>
+          <t>318961</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>904706</t>
+          <t>763210</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>382183; 431230</t>
+          <t>420698; 465030</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>433453; 550875</t>
+          <t>302696; 333654</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>842106; 1007388</t>
+          <t>731106; 788270</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>186284</t>
+          <t>221682</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>294192</t>
+          <t>333264</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>480476</t>
+          <t>554946</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>173672; 198171</t>
+          <t>206208; 232856</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>212150; 324999</t>
+          <t>316648; 343765</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>391916; 514274</t>
+          <t>534054; 571449</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>69654</t>
+          <t>73843</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>325345</t>
+          <t>361537</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>394998</t>
+          <t>435379</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>51025; 87362</t>
+          <t>56644; 90080</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>306463; 341509</t>
+          <t>343670; 377954</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>366408; 416788</t>
+          <t>407912; 457484</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1195131</t>
+          <t>1306236</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1465472</t>
+          <t>1401676</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2660603</t>
+          <t>2707911</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1153854; 1232206</t>
+          <t>1257855; 1341807</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1384781; 1580876</t>
+          <t>1369324; 1430960</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2576781; 2806557</t>
+          <t>2657470; 2759625</t>
         </is>
       </c>
     </row>
